--- a/www/download/COUNTRY.JPN.rpPE.xlsx
+++ b/www/download/COUNTRY.JPN.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Japão</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>93.4579392724969</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>108.69565009423</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>120.772951100123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>130.378093106072</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>113.895220219769</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>107.758622330519</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>121.359218118173</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>125.156448030675</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>115.740744752688</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>108.108106778803</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>110.011003151538</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>116.279065778384</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>117.647052871306</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>103.094909107448</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>93.454450428309</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>66.858</t>
+          <t>-0.480070672228191</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>66.907</t>
+          <t>-0.372956202692721</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.374</t>
+          <t>-0.316970369984686</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>-0.262413053702971</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>65.664</t>
+          <t>-0.323866305978014</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>65.253</t>
+          <t>-0.349386927605038</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>-0.283250045172117</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>63.748</t>
+          <t>-0.252214781122492</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>63.537</t>
+          <t>-0.251508286472921</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>63.677</t>
+          <t>-0.25416832361564</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>63.917</t>
+          <t>-0.216794001492017</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>64.197</t>
+          <t>-0.131887558489813</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>64.438</t>
+          <t>-0.0387641480466465</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>63.045</t>
+          <t>-0.0959277573647993</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>58.129</t>
+          <t>-0.212560643028769</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>53.767</t>
+          <t>-0.612358300108422</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.252</t>
+          <t>-0.539689843978672</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>54.767</t>
+          <t>-0.510567548700313</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.304</t>
+          <t>-0.479505989915092</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>53.699</t>
+          <t>-0.528693198474534</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>53.778</t>
+          <t>-0.55814404911699</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>-0.50874418027465</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53.22</t>
+          <t>-0.47673455247496</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>53.165</t>
+          <t>-0.488128515100485</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>53.333</t>
+          <t>-0.479866330213434</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>53.676</t>
+          <t>-0.453897137522751</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>54.501</t>
+          <t>-0.397493606806131</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>54.736</t>
+          <t>-0.324868274014759</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>53.523</t>
+          <t>-0.357744929698309</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>49.344</t>
+          <t>-0.445698599104027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>128222.472</t>
+          <t>-0.866730441398221</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>128765.062</t>
+          <t>-0.837589209608557</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>127817.187</t>
+          <t>-0.829608921127738</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>124807.729</t>
+          <t>-0.827401480043403</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>121678.753</t>
+          <t>-0.847979795404924</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>121538.02</t>
+          <t>-0.863555305994096</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120328.064</t>
+          <t>-0.847998248873062</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>117808.29</t>
+          <t>-0.834111434137592</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>117674.143</t>
+          <t>-0.822758723857598</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>117553.502</t>
+          <t>-0.827235143893816</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>115915.217</t>
+          <t>-0.811873333237655</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>117204.754</t>
+          <t>-0.78439727886129</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>117623.105</t>
+          <t>-0.743730111456152</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>114963.431</t>
+          <t>-0.745558090308398</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>105856.42</t>
+          <t>-0.780039936776083</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>102785.336</t>
+          <t>691286220609.538</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>103927.218</t>
+          <t>662199823429.589</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>103369.217</t>
+          <t>652747845528.782</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>101246.989</t>
+          <t>638330727561.461</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>99076.807</t>
+          <t>671141781118.243</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>100177.904</t>
+          <t>729510072007.579</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>99460.607</t>
+          <t>715154960682.232</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>97626.584</t>
+          <t>680303626995.328</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>97944.352</t>
+          <t>639126860052.986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>98147.153</t>
+          <t>700043647100.064</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>96831.355</t>
+          <t>686845557016.441</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>99350.695</t>
+          <t>688512627588.751</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>99761.612</t>
+          <t>641538713240.349</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>97421.377</t>
+          <t>634086919305.62</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>89716.478</t>
+          <t>547907343508.61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>944737104536.676</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>791397752940.208</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>744220688684.43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>721233990850.369</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>801281523516.931</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>894816495982.734</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>809197646071.101</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>745382043559.537</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>691744425404.328</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>725180646902.837</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>667383503600.021</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>600508284510.784</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>506088331843.893</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>498693200902.056</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>535935060943.867</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>3003637.81021505</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>3281470.83009811</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>3533968.13729337</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>59.19</t>
+          <t>3863626.216336</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>3738992.5680159</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>3795306.46945805</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>4323806.43938707</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>59.19</t>
+          <t>4361868.34854323</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>3802246.67045806</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.66</t>
+          <t>3783415.59044006</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>3675264.81376283</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>3775868.61542989</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>3394059.6439072</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2924074.18578843</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2741920.78990832</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>920336.348612209</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>921899.231743729</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>910684.985454204</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>888859.514594669</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>907581.088431255</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>924508.670914993</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>887477.338347363</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>876946.489822266</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>926815.634230419</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>1012828.47266606</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1055493.00040127</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1096551.58482507</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1211046.76488684</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1261484.683964</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1079944.62190177</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>2280847.13566858</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>2210214.6820699</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>2131537.30123213</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.98</t>
+          <t>1977600.53129695</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>2105004.09595694</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>2226049.04820688</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>2105048.0683632</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>2055934.91207551</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>2239306.56924266</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>2547939.02087754</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>2708656.52073043</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>2887217.10438544</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>3179924.17111033</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>3571170.02788363</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>2842540.61787208</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>-0.603476598945362</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>-0.521917432667577</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>-0.483618121773505</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>-0.442332657483376</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>-0.489442213243651</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>-0.512226514507224</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>54.51</t>
+          <t>-0.453933614466351</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>-0.418261569257293</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>-0.419835000968224</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>-0.413010909355426</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>-0.381042216280413</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>-0.315008140041871</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>53.72</t>
+          <t>-0.236296964305679</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>-0.276865354730362</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>53.51</t>
+          <t>-0.371666670032418</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>1238577.27673467</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>1135587.3850905</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1055483.71619686</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>992382.890236023</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1182799.27149798</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>1310499.49508807</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1202462.87013806</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1148355.30447645</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>1255511.94484904</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1361019.55503367</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1386771.57974616</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1361629.24965676</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1401105.22131454</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1684818.85989241</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>1822179.78509325</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>93.4579392724969</t>
+          <t>17571.0749609647</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>108.69565009423</t>
+          <t>14587.5519622504</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>120.772951100123</t>
+          <t>13588.9018316502</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>130.378093106072</t>
+          <t>13281.517306282</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>113.895220219769</t>
+          <t>14921.818339696</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>107.758622330519</t>
+          <t>16639.0163100475</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>121.359218118173</t>
+          <t>15040.7990964314</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>125.156448030675</t>
+          <t>14005.6486411855</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>115.740744752688</t>
+          <t>13011.3313044143</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>108.108106778803</t>
+          <t>13597.1046680009</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>110.011003151538</t>
+          <t>12433.5423370037</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>116.279065778384</t>
+          <t>11018.3014619755</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>117.647052871306</t>
+          <t>9245.96096587167</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>103.094909107448</t>
+          <t>9317.39855178498</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>93.454450428309</t>
+          <t>10861.2657353223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.745</t>
+          <t>232340051517.396</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>194464779374.074</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>173661181510.607</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>173814150623.601</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.207</t>
+          <t>199462529113.608</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>231876609502.803</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>206508785218.868</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.957</t>
+          <t>204074633736.581</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.093</t>
+          <t>207479073873.02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>241075265051.482</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>227732649177.918</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>206563327267.641</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2.184</t>
+          <t>175042656347.731</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.427</t>
+          <t>157830467874.858</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>148766025771.578</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.161</t>
+          <t>223641280232.566</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>188848950239.683</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>167140693364.033</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>168468770679</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>192771746758.434</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.676</t>
+          <t>218754442211.737</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.342</t>
+          <t>199688589905.283</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>197397215585.1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.363</t>
+          <t>193956423667.785</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.558</t>
+          <t>223728792920.839</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.537</t>
+          <t>209054455771.973</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.438</t>
+          <t>190648315739.457</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2.439</t>
+          <t>161214303606.731</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>145924737764.948</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>138096196316.174</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21.289</t>
+          <t>8698771284.83043</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18.315</t>
+          <t>5615829134.39045</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.234</t>
+          <t>6520488146.57332</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.762</t>
+          <t>5345379944.6015</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>16.629</t>
+          <t>6690782355.17388</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>13122167291.066</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14.986</t>
+          <t>6820195313.58484</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14.368</t>
+          <t>6677418151.48019</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>15.445</t>
+          <t>13522650205.235</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16.527</t>
+          <t>17346472130.6432</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>16.431</t>
+          <t>18678193405.9451</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>15.696</t>
+          <t>15915011528.184</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>13828352741</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>18.261</t>
+          <t>11905730109.9101</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>19.296</t>
+          <t>10669829455.4045</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9.871</t>
+          <t>6967.34240370771</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.653</t>
+          <t>6974.0542932078</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.989</t>
+          <t>7017.06265086299</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7.179</t>
+          <t>7406.6684607828</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.074</t>
+          <t>7618.45054589548</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>8116.07098072302</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7.611</t>
+          <t>8213.27479812607</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7.256</t>
+          <t>8147.62406205699</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.844</t>
+          <t>7548.71901362766</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.568</t>
+          <t>7981.35210446897</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8.632</t>
+          <t>7695.83780869547</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.377</t>
+          <t>7547.44681201797</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8.489</t>
+          <t>7061.16845754739</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9.696</t>
+          <t>6737.73369658087</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9.388</t>
+          <t>6824.49526713786</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>8439.35501723023</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>8408.45397778065</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>8450.23532048556</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>8956.28321147146</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.353</t>
+          <t>9177.41883723679</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.637</t>
+          <t>9761.80382482475</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.048</t>
+          <t>9874.16332344029</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.886</t>
+          <t>9741.09797342224</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>8963.22525167705</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.555</t>
+          <t>9446.91701982021</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4.528</t>
+          <t>9102.28749158383</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4.309</t>
+          <t>8909.16818147475</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>4.311</t>
+          <t>8295.76036594493</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.786</t>
+          <t>7844.52031072051</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.915</t>
+          <t>7886.60916343384</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-48.01</t>
+          <t>483962.022809018</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-37.3</t>
+          <t>455957.578364688</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-31.7</t>
+          <t>464289.436779155</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-26.24</t>
+          <t>422241.077273735</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-32.39</t>
+          <t>449039.96309977</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-34.94</t>
+          <t>512774.676338099</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>433152.032599372</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-25.22</t>
+          <t>446074.530739801</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-25.15</t>
+          <t>508743.94452293</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>613148.226897316</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-21.68</t>
+          <t>653686.58796679</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>703104.29234662</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>772058.453217856</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>861051.099931609</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-21.26</t>
+          <t>640035.862377991</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-61.24</t>
+          <t>43181313239.8406</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-53.97</t>
+          <t>43465507576.0546</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-51.06</t>
+          <t>47611573720.9752</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>48599279535.9207</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>50351239873.1663</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-55.81</t>
+          <t>57356597383.4878</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-50.87</t>
+          <t>57136179506.7702</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-47.67</t>
+          <t>58927047519.5166</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-48.81</t>
+          <t>56195132188.6551</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>67127650167.9481</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>69275574684.4392</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-39.75</t>
+          <t>75692243967.7454</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>75598142966.8452</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-35.77</t>
+          <t>74817793726.9738</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-44.57</t>
+          <t>52867237104.8432</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-86.67</t>
+          <t>361449.028162005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-83.76</t>
+          <t>378258.286699501</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-82.96</t>
+          <t>364293.55567603</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-82.74</t>
+          <t>305787.918290855</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-84.8</t>
+          <t>332977.695824036</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-86.36</t>
+          <t>393855.253197297</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-84.8</t>
+          <t>364150.906360956</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-83.41</t>
+          <t>353103.882198101</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-82.28</t>
+          <t>393676.23411606</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-82.72</t>
+          <t>467719.977847277</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-81.19</t>
+          <t>530733.092738067</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-78.44</t>
+          <t>591311.642769675</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-74.37</t>
+          <t>639123.642918831</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>782839.984506907</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-78</t>
+          <t>569068.802394461</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>564236.281</t>
+          <t>228291645133.787</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>562582.126</t>
+          <t>209005106969.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>569323.419</t>
+          <t>186500514885.754</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>596306.023</t>
+          <t>177427170061.516</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>602622.338</t>
+          <t>202248428489.349</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>636982.89</t>
+          <t>237728227811.304</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>639446.669</t>
+          <t>232010696821.147</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>620971.373</t>
+          <t>221069055866.213</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>569492.566</t>
+          <t>218481023182.513</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>601547.116</t>
+          <t>252887596365.618</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>581786.819</t>
+          <t>254307598045.092</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>571945.772</t>
+          <t>247362050992.226</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>534564.389</t>
+          <t>215789185030.151</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>494557.875</t>
+          <t>214827149971.838</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>458442.471</t>
+          <t>183529205319.046</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>374610.37</t>
+          <t>122512.994647013</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>378353.47</t>
+          <t>77699.2916651878</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>384302.077</t>
+          <t>99995.8811031255</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>402208.643</t>
+          <t>116453.158982879</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>409100.521</t>
+          <t>116062.267275734</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>436467.761</t>
+          <t>118919.423140802</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>441875.634</t>
+          <t>69001.1262384158</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>433617.38</t>
+          <t>92970.6485417003</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>401325.904</t>
+          <t>115067.71040687</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>425673.128</t>
+          <t>145428.24905004</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>413082.214</t>
+          <t>122953.495228723</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>411343.287</t>
+          <t>111792.649576946</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>386501.195</t>
+          <t>132934.810299025</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>360622.331</t>
+          <t>78211.1154247029</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>336745.861</t>
+          <t>70967.05998353</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>691286.221</t>
+          <t>-185110331893.947</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>662199.823</t>
+          <t>-165539599393.146</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>652747.846</t>
+          <t>-138888941164.778</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>638330.728</t>
+          <t>-128827890525.595</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>671141.781</t>
+          <t>-151897188616.183</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>729510.072</t>
+          <t>-180371630427.817</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>715154.961</t>
+          <t>-174874517314.377</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>680303.627</t>
+          <t>-162142008346.697</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>639126.86</t>
+          <t>-162285890993.858</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>700043.647</t>
+          <t>-185759946197.67</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>686845.557</t>
+          <t>-185032023360.652</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>688512.628</t>
+          <t>-171669807024.48</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>641538.713</t>
+          <t>-140191042063.306</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>634086.919</t>
+          <t>-140009356244.865</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>547907.344</t>
+          <t>-130661968214.203</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>2469602.19314</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2150162.69387</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>1958081.07133</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>1762337.40213</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>1976049.10429</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.226</t>
+          <t>2070706.36648</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>1760254.25355</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>1666078.9694</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.239</t>
+          <t>1800835.6686</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.548</t>
+          <t>1964591.70782</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.709</t>
+          <t>1935959.52168</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.887</t>
+          <t>1824377.36754</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1827858.90132</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.571</t>
+          <t>1965124.84046</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.843</t>
+          <t>1988539.81573</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>278938.394</t>
+          <t>0.0394434673608987</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>276209.145</t>
+          <t>0.0418010038489623</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>278882.13</t>
+          <t>0.0430304205892913</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>286906.446</t>
+          <t>0.0409042669490046</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>289365.512</t>
+          <t>0.0389487529557792</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>302975.529</t>
+          <t>0.0379092855945517</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>301505.619</t>
+          <t>0.0336576202573701</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>290179.36</t>
+          <t>0.0366244713755246</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>264525.087</t>
+          <t>0.0376119565346933</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>278273.59</t>
+          <t>0.0384392310000728</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>267645.85</t>
+          <t>0.0368109342702985</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>261493.883</t>
+          <t>0.0324893574469158</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>244324.5</t>
+          <t>0.0300305437030943</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>223985.677</t>
+          <t>0.0211981156577775</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>208162.228</t>
+          <t>0.0172100433782819</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2745397.56350226</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>2356418.57498836</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>2155235.27917576</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>1967747.36004907</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>2207154.36040258</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>2355518.11130577</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>2070012.8644661</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>1956912.12619623</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>2092714.68105092</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>2272852.69144693</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>2250071.87505063</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>2181417.80457924</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>2184132.6284078</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>2427079.55996368</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2467893.18097585</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>944737.105</t>
+          <t>3161322.34066248</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>791397.753</t>
+          <t>2705927.70396172</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>744220.689</t>
+          <t>2473218.33201866</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>721233.991</t>
+          <t>2251829.38971421</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>801281.524</t>
+          <t>2522696.35008506</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>894816.496</t>
+          <t>2675664.46797961</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>809197.646</t>
+          <t>2341509.78794984</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>745382.044</t>
+          <t>2211861.0252521</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>691744.425</t>
+          <t>2362881.4347047</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>725180.647</t>
+          <t>2558230.46020092</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>667383.504</t>
+          <t>2536580.45629792</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>600508.285</t>
+          <t>2437547.78207593</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>506088.332</t>
+          <t>2439014.46378651</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>498693.201</t>
+          <t>2711916.13868508</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>535935.061</t>
+          <t>2756086.66383692</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-60.35</t>
+          <t>21289271.5883617</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-52.19</t>
+          <t>18315178.6879104</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-48.36</t>
+          <t>16233901.8565931</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-44.23</t>
+          <t>14761559.2202773</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-48.94</t>
+          <t>16628739.7894945</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-51.22</t>
+          <t>17169878.1278504</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>14986316.6725713</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-41.83</t>
+          <t>14367934.1551703</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>15445118.637219</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-41.3</t>
+          <t>16527248.3586938</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-38.1</t>
+          <t>16431446.4708916</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-31.5</t>
+          <t>15695785.5143952</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>15670296.4921833</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-27.69</t>
+          <t>18261131.6571798</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-37.17</t>
+          <t>19296059.8571648</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.004</t>
+          <t>3161322.34066248</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.281</t>
+          <t>3162003.21704048</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.534</t>
+          <t>3190264.114627</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.864</t>
+          <t>3132792.50756439</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.739</t>
+          <t>3111508.39892445</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3175021.90317712</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.324</t>
+          <t>3177330.7508373</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.362</t>
+          <t>3158907.6323282</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.802</t>
+          <t>3202549.61161134</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.783</t>
+          <t>3293486.32002534</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3402767.23963482</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.776</t>
+          <t>3502464.42346657</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.394</t>
+          <t>3608715.10270966</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.924</t>
+          <t>3568185.74207821</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.742</t>
+          <t>3228363.12701674</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2745397.56350226</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2751518.43333455</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2779033.86443456</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2738093.4749526</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2724023.03041981</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2798438.82226227</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2811371.36632261</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2795791.87458553</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2843017.58644692</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2936298.47565236</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3028408.70367268</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3144687.39563941</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>3243967.67620102</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3209106.84218701</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2900728.67846221</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2078299.96576752</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1901180.23991828</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1754035.34089134</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1596193.64916579</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1830467.94952494</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1961397.30866039</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1706866.62576016</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1674573.2976679</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1836433.0757053</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1996314.27248908</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1991628.47575208</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1871575.23564407</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1871692.7449635</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2071920.44080321</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2154265.81226498</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>374610369793.394</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>378353469506.765</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>384302077037.881</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>402208643010.184</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>409100521215.56</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>436467761121.931</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>441875633772.383</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>433617380324.117</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>401325903894.938</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>425673128478.541</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>413082214279.282</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>411343286727.307</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>386501195358.656</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>360622330932.688</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>336745861489.239</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>564236281258.321</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>562582126077.215</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>569323419185.915</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>596306022650.903</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>602622337720.212</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>636982890210.875</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>639446668675.442</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>620971373147.59</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>569492565544.409</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>601547115847.066</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>581786819495.459</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>571945771910.645</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>534564389231.507</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>494557875479.782</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>458442470671.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>278938393622.43</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>276209145397.969</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>278882129750.683</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>286906446307.961</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>289365512099.909</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>302975528609.354</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>301505619064.406</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>290179360349.808</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>264525087493.508</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>278273589784.634</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>267645850346.53</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>261493883438.054</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>244324500023.567</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>223985677175.946</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>208162228255.356</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>66857749.2126289</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>66906725.9645875</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>67373676.3052891</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>66579630.0285745</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>65663597.6201838</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>65252580.5313763</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>64759579.8985275</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>63747574.9491338</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>63536567.4245277</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>63676553.3755598</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>63916550.6509646</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>64197437.9942584</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>64438263.1188283</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>63045011.7904479</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>58129224.001234</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>53766608.2829578</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>54251580.7304874</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>54766801.4608104</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>54303584.0121397</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>53698651.5500802</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>53778208.9583263</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>53800176.4988066</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>53220101.5929844</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>53164769.1708257</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>53333460.660155</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>53676055.1024794</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>54500985.1639254</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>54736152.7603184</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>53522793.7423068</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>49343702.106554</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>128222471703.372</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>128765062457.942</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>127817186581.938</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>124807729306.285</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>121678752876.065</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>121538020243.119</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>120328063648.719</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>117808290223.311</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>117674143014.12</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>117553502189.724</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>115915216876.385</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>117204754014.252</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>117623105374.446</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>114963431160.589</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>105856420383.388</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>102785336309.266</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>103927217679.788</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>103369217150.21</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>101246988677.691</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>99076807477.4328</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>100177904290.721</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>99460607407.5732</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>97626583840.2885</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>97944352454.1957</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>98147153379.7101</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>96831355076.2254</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>99350695264.1884</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>99761612250.3796</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>97421377310.7341</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>89716477994.8995</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.230758021741052</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.238337633636048</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.241076805747217</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.251387734325517</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.256340884219462</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.260870477022473</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.271140539201546</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.285334184329508</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.286944809377974</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.290876712969125</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.582530546331134</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.586060041193847</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.590377919030962</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.591940917362233</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.595380718738523</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.598079257768512</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.598630257895856</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.591938496678375</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.598516075120748</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.596621977659668</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.158140003356385</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.147030896598676</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.139973846650393</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.128099919740821</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.119706968470586</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.112478836637586</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.10165777433117</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0941558904206893</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0859676869298493</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0839298807997789</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.337065498109691</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.346933223690957</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.354699529306754</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.369785855954179</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.37862499004562</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.3867719414465</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.397458895979981</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.409567225612581</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.40946676846145</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.41240855468034</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.410323906721809</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.40987346388389</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.406010462454583</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.403814469180385</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.407081832021567</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.579479185858004</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.573088198986263</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.569186802462386</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.560689239369208</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.556463689335333</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.552015854929772</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.54507492657662</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.534847739951375</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.535379243377685</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.533923586119178</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.535350659287623</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.5350163957751</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.537151580968896</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.538115106113555</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.535107659757911</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0548838874608763</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0514071487513508</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0475422396594321</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.040953476105184</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0363398920476187</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0326407750522996</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0288947488719708</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0270136058646161</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0265825595894368</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0250964306290534</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0257540054191387</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0265387117695811</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0282665280050932</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0294989961346314</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0292390796490938</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9871402.09181</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8653218.418</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>7988888.18361</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7179054.14357</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8074125.72561</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8689624.72806</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7611125.04837</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7256470.83011</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7844053.41652</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8567572.2029</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>8631934.89718</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8376839.74448</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>8489190.97734</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>9695796.51719</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>9388243.2637</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5239622.30643</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4607107.94388</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>4227253.67291</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3848023.03888</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4353164.29961</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4637061.77664</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4048376.41371</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3886434.32292</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4199314.51041</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4554544.73269</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>4528208.93205</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>4309123.01772</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>4310707.20875</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4785564.42746</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4915208.0621</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1989651471.99018</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1983884302.2851</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1980909167.36731</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1976859801.86027</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1968606741.73799</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1962344651.4736</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1959208836.15363</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1965164273.02802</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1965416581.54312</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1969463696.72909</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1977047990.64659</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1984685690.04331</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1991084750.73126</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1994399618.16927</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1979901624.26518</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
